--- a/output/stock_quant_scores/AMD_info.xlsx
+++ b/output/stock_quant_scores/AMD_info.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FQ2"/>
+  <dimension ref="A1:FU2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1066,225 +1066,245 @@
       </c>
       <c r="DY1" s="1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketTime</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EN1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EO1" s="1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampStart</t>
+        </is>
+      </c>
+      <c r="EP1" s="1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EQ1" s="1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="ER1" s="1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="ES1" s="1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="ET1" s="1" t="inlineStr">
+        <is>
+          <t>epsCurrentYear</t>
+        </is>
+      </c>
+      <c r="EU1" s="1" t="inlineStr">
+        <is>
+          <t>priceEpsCurrentYear</t>
+        </is>
+      </c>
+      <c r="EV1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EW1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EX1" s="1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EY1" s="1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EZ1" s="1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="FA1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="FB1" s="1" t="inlineStr">
+        <is>
+          <t>averageAnalystRating</t>
+        </is>
+      </c>
+      <c r="FC1" s="1" t="inlineStr">
+        <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EA1" s="1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EB1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EC1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="ED1" s="1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EE1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EF1" s="1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EG1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EH1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EI1" s="1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EJ1" s="1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="EK1" s="1" t="inlineStr">
+      <c r="FD1" s="1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="FE1" s="1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="FF1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="FG1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketPrice</t>
+        </is>
+      </c>
+      <c r="FH1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChange</t>
+        </is>
+      </c>
+      <c r="FI1" s="1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="EL1" s="1" t="inlineStr">
+      <c r="FJ1" s="1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="EM1" s="1" t="inlineStr">
+      <c r="FK1" s="1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="EN1" s="1" t="inlineStr">
+      <c r="FL1" s="1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="EO1" s="1" t="inlineStr">
+      <c r="FM1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="EP1" s="1" t="inlineStr">
+      <c r="FN1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="EQ1" s="1" t="inlineStr">
+      <c r="FO1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="ER1" s="1" t="inlineStr">
+      <c r="FP1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="ES1" s="1" t="inlineStr">
+      <c r="FQ1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="ET1" s="1" t="inlineStr">
+      <c r="FR1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="EU1" s="1" t="inlineStr">
+      <c r="FS1" s="1" t="inlineStr">
         <is>
           <t>earningsTimestamp</t>
         </is>
       </c>
-      <c r="EV1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EW1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EX1" s="1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampStart</t>
-        </is>
-      </c>
-      <c r="EY1" s="1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EZ1" s="1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="FA1" s="1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="FB1" s="1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="FC1" s="1" t="inlineStr">
-        <is>
-          <t>epsCurrentYear</t>
-        </is>
-      </c>
-      <c r="FD1" s="1" t="inlineStr">
-        <is>
-          <t>priceEpsCurrentYear</t>
-        </is>
-      </c>
-      <c r="FE1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="FF1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="FG1" s="1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="FH1" s="1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="FI1" s="1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="FJ1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="FK1" s="1" t="inlineStr">
-        <is>
-          <t>averageAnalystRating</t>
-        </is>
-      </c>
-      <c r="FL1" s="1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="FM1" s="1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="FN1" s="1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="FO1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="FP1" s="1" t="inlineStr">
+      <c r="FT1" s="1" t="inlineStr">
         <is>
           <t>displayName</t>
         </is>
       </c>
-      <c r="FQ1" s="1" t="inlineStr">
+      <c r="FU1" s="1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -1410,28 +1430,28 @@
         <v>2</v>
       </c>
       <c r="AC2" t="n">
-        <v>160.9</v>
+        <v>161.27</v>
       </c>
       <c r="AD2" t="n">
-        <v>162.99</v>
+        <v>160.58</v>
       </c>
       <c r="AE2" t="n">
-        <v>158.43</v>
+        <v>157.0501</v>
       </c>
       <c r="AF2" t="n">
-        <v>165.1</v>
+        <v>162.11</v>
       </c>
       <c r="AG2" t="n">
-        <v>160.9</v>
+        <v>161.27</v>
       </c>
       <c r="AH2" t="n">
-        <v>162.99</v>
+        <v>160.58</v>
       </c>
       <c r="AI2" t="n">
-        <v>158.43</v>
+        <v>157.05</v>
       </c>
       <c r="AJ2" t="n">
-        <v>165.1</v>
+        <v>162.11</v>
       </c>
       <c r="AK2" t="n">
         <v>798940800</v>
@@ -1443,40 +1463,40 @@
         <v>1.916</v>
       </c>
       <c r="AN2" t="n">
-        <v>96.95508599999999</v>
+        <v>95.48504</v>
       </c>
       <c r="AO2" t="n">
-        <v>31.74804</v>
+        <v>31.266668</v>
       </c>
       <c r="AP2" t="n">
-        <v>29975798</v>
+        <v>30244953</v>
       </c>
       <c r="AQ2" t="n">
-        <v>29974992</v>
+        <v>30244953</v>
       </c>
       <c r="AR2" t="n">
-        <v>55082100</v>
+        <v>53667784</v>
       </c>
       <c r="AS2" t="n">
-        <v>47597810</v>
+        <v>43808560</v>
       </c>
       <c r="AT2" t="n">
-        <v>47597810</v>
+        <v>43808560</v>
       </c>
       <c r="AU2" t="n">
-        <v>151.55</v>
+        <v>159.26</v>
       </c>
       <c r="AV2" t="n">
-        <v>167.9</v>
+        <v>159.69</v>
       </c>
       <c r="AW2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY2" t="n">
-        <v>262762725376</v>
+        <v>258778660864</v>
       </c>
       <c r="AZ2" t="n">
         <v>76.48</v>
@@ -1491,13 +1511,13 @@
         <v>1.61</v>
       </c>
       <c r="BD2" t="n">
-        <v>8.876296999999999</v>
+        <v>8.742521999999999</v>
       </c>
       <c r="BE2" t="n">
-        <v>165.26</v>
+        <v>165.3702</v>
       </c>
       <c r="BF2" t="n">
-        <v>126.85295</v>
+        <v>127.1413</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -1514,7 +1534,7 @@
         <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>259134554112</v>
+        <v>256797655040</v>
       </c>
       <c r="BL2" t="n">
         <v>0.095740005</v>
@@ -1526,31 +1546,31 @@
         <v>1622843689</v>
       </c>
       <c r="BO2" t="n">
-        <v>39165658</v>
+        <v>41767201</v>
       </c>
       <c r="BP2" t="n">
-        <v>42120268</v>
+        <v>47900122</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1753920000</v>
+        <v>1755216000</v>
       </c>
       <c r="BR2" t="n">
-        <v>1756425600</v>
+        <v>1757894400</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.0241</v>
+        <v>0.0257</v>
       </c>
       <c r="BT2" t="n">
         <v>0.00504</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.69391</v>
+        <v>0.69408</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.61</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.0242</v>
+        <v>0.025899999</v>
       </c>
       <c r="BX2" t="n">
         <v>1622843689</v>
@@ -1559,7 +1579,7 @@
         <v>36.785</v>
       </c>
       <c r="BZ2" t="n">
-        <v>4.401658</v>
+        <v>4.3349195</v>
       </c>
       <c r="CA2" t="n">
         <v>1735344000</v>
@@ -1591,16 +1611,16 @@
         <v>966902400</v>
       </c>
       <c r="CJ2" t="n">
-        <v>8.755000000000001</v>
+        <v>8.676</v>
       </c>
       <c r="CK2" t="n">
-        <v>47.03</v>
+        <v>46.606</v>
       </c>
       <c r="CL2" t="n">
-        <v>-0.0069127083</v>
+        <v>-0.028156996</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.16333759</v>
+        <v>0.1529237</v>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
@@ -1608,7 +1628,7 @@
         </is>
       </c>
       <c r="CO2" t="n">
-        <v>161.9</v>
+        <v>159.46</v>
       </c>
       <c r="CP2" t="n">
         <v>230</v>
@@ -1730,169 +1750,181 @@
       </c>
       <c r="DX2" t="inlineStr">
         <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="DY2" t="b">
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="EB2" t="n">
+        <v>1758931188</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>1758916801</v>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>NMS</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>finmb_168864</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>America/New_York</t>
+        </is>
+      </c>
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>EDT</t>
+        </is>
+      </c>
+      <c r="EH2" t="n">
+        <v>-14400000</v>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>us_market</t>
+        </is>
+      </c>
+      <c r="EJ2" t="b">
         <v>0</v>
       </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>NMS</t>
-        </is>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>finmb_168864</t>
-        </is>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>America/New_York</t>
-        </is>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>EDT</t>
-        </is>
-      </c>
-      <c r="ED2" t="n">
-        <v>-14400000</v>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>us_market</t>
-        </is>
-      </c>
-      <c r="EF2" t="b">
+      <c r="EK2" t="n">
+        <v>-1.12234</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>159.46</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>1762286400</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>1762286400</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>1754427600</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>1754427600</v>
+      </c>
+      <c r="EQ2" t="b">
+        <v>1</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>3.89671</v>
+      </c>
+      <c r="EU2" t="n">
+        <v>40.921703</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>-5.910187</v>
+      </c>
+      <c r="EW2" t="n">
+        <v>-0.03573913</v>
+      </c>
+      <c r="EX2" t="n">
+        <v>32.31871</v>
+      </c>
+      <c r="EY2" t="n">
+        <v>0.2541952</v>
+      </c>
+      <c r="EZ2" t="n">
+        <v>15</v>
+      </c>
+      <c r="FA2" t="n">
         <v>0</v>
       </c>
-      <c r="EG2" t="n">
-        <v>0.63082623</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>161.915</v>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>Advanced Micro Devices, Inc.</t>
-        </is>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>Advanced Micro Devices, Inc.</t>
-        </is>
-      </c>
-      <c r="EK2" t="n">
-        <v>1.0149994</v>
-      </c>
-      <c r="EL2" t="inlineStr">
-        <is>
-          <t>158.43 - 165.1</t>
-        </is>
-      </c>
-      <c r="EM2" t="inlineStr">
+      <c r="FB2" t="inlineStr">
+        <is>
+          <t>1.7 - Buy</t>
+        </is>
+      </c>
+      <c r="FC2" t="b">
+        <v>0</v>
+      </c>
+      <c r="FD2" t="b">
+        <v>1</v>
+      </c>
+      <c r="FE2" t="n">
+        <v>322151400000</v>
+      </c>
+      <c r="FF2" t="n">
+        <v>-0.2884778</v>
+      </c>
+      <c r="FG2" t="n">
+        <v>159</v>
+      </c>
+      <c r="FH2" t="n">
+        <v>-0.4600067</v>
+      </c>
+      <c r="FI2" t="n">
+        <v>-1.81</v>
+      </c>
+      <c r="FJ2" t="inlineStr">
+        <is>
+          <t>157.05 - 162.11</t>
+        </is>
+      </c>
+      <c r="FK2" t="inlineStr">
         <is>
           <t>NasdaqGS</t>
         </is>
       </c>
-      <c r="EN2" t="n">
-        <v>55082100</v>
-      </c>
-      <c r="EO2" t="n">
-        <v>85.43499</v>
-      </c>
-      <c r="EP2" t="n">
-        <v>1.1170893</v>
-      </c>
-      <c r="EQ2" t="inlineStr">
+      <c r="FL2" t="n">
+        <v>53667784</v>
+      </c>
+      <c r="FM2" t="n">
+        <v>82.98</v>
+      </c>
+      <c r="FN2" t="n">
+        <v>1.0849895</v>
+      </c>
+      <c r="FO2" t="inlineStr">
         <is>
           <t>76.48 - 186.65</t>
         </is>
       </c>
-      <c r="ER2" t="n">
-        <v>-24.735</v>
-      </c>
-      <c r="ES2" t="n">
-        <v>-0.13252077</v>
-      </c>
-      <c r="ET2" t="n">
-        <v>-0.6912708</v>
-      </c>
-      <c r="EU2" t="n">
+      <c r="FP2" t="n">
+        <v>-27.189987</v>
+      </c>
+      <c r="FQ2" t="n">
+        <v>-0.14567366</v>
+      </c>
+      <c r="FR2" t="n">
+        <v>-2.8156996</v>
+      </c>
+      <c r="FS2" t="n">
         <v>1754424000</v>
       </c>
-      <c r="EV2" t="n">
-        <v>1762286400</v>
-      </c>
-      <c r="EW2" t="n">
-        <v>1762286400</v>
-      </c>
-      <c r="EX2" t="n">
-        <v>1754427600</v>
-      </c>
-      <c r="EY2" t="n">
-        <v>1754427600</v>
-      </c>
-      <c r="EZ2" t="b">
-        <v>1</v>
-      </c>
-      <c r="FA2" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="FB2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="FC2" t="n">
-        <v>3.89671</v>
-      </c>
-      <c r="FD2" t="n">
-        <v>41.55172</v>
-      </c>
-      <c r="FE2" t="n">
-        <v>-3.3450012</v>
-      </c>
-      <c r="FF2" t="n">
-        <v>-0.020240841</v>
-      </c>
-      <c r="FG2" t="n">
-        <v>35.062042</v>
-      </c>
-      <c r="FH2" t="n">
-        <v>0.2763991</v>
-      </c>
-      <c r="FI2" t="n">
-        <v>15</v>
-      </c>
-      <c r="FJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="FK2" t="inlineStr">
-        <is>
-          <t>1.7 - Buy</t>
-        </is>
-      </c>
-      <c r="FL2" t="b">
-        <v>1</v>
-      </c>
-      <c r="FM2" t="n">
-        <v>322151400000</v>
-      </c>
-      <c r="FN2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="FO2" t="n">
-        <v>1758740015</v>
-      </c>
-      <c r="FP2" t="inlineStr">
+      <c r="FT2" t="inlineStr">
         <is>
           <t>Advanced Micro Devices</t>
         </is>
       </c>
-      <c r="FQ2" t="n">
-        <v>0.4975</v>
+      <c r="FU2" t="n">
+        <v>0.4931</v>
       </c>
     </row>
   </sheetData>
